--- a/StriversSheet/leetcode_problem_links_topics_plain.xlsx
+++ b/StriversSheet/leetcode_problem_links_topics_plain.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NFRAC\Laboratory\Projects\Java\LeetCodeSolutions\StriversSheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9724EAFC-FCF5-4382-A2E8-F5FB54808919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38A5A7DE-8F89-4E53-970F-82657E97D287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1080,7 +1080,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1095,6 +1095,24 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1130,14 +1148,14 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1352,1409 +1370,1409 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C130"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="64.83203125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="112.1640625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="81.6640625" style="5" customWidth="1"/>
-    <col min="4" max="16384" width="8.6640625" style="5"/>
+    <col min="1" max="1" width="64.83203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="112.1640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="81.6640625" style="3" customWidth="1"/>
+    <col min="4" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="4" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="4" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="4" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="4" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="4" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="4" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="4" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="4" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="4" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="4" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="4" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="4" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="4" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="4" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="4" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="4" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="4" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="4" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="4" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="4" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="4" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="4" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="4" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="4" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="4" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="3" t="s">
+      <c r="A50" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="4" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="4" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="3" t="s">
+      <c r="A53" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="4" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="3" t="s">
+      <c r="A54" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="4" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" s="4" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="3" t="s">
+      <c r="A56" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C56" s="4" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="4" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="3" t="s">
+      <c r="A58" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C58" s="4" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C59" s="4" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="3" t="s">
+      <c r="A60" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C60" s="4" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="3" t="s">
+      <c r="A61" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C61" s="4" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="62" spans="1:3">
-      <c r="A62" s="3" t="s">
+      <c r="A62" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="4" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="3" t="s">
+      <c r="A63" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C63" s="4" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="14.5" customHeight="1">
-      <c r="A64" s="3" t="s">
+      <c r="A64" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="4" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="65" spans="1:3">
-      <c r="A65" s="3" t="s">
+      <c r="A65" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C65" s="4" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="66" spans="1:3">
-      <c r="A66" s="3" t="s">
+      <c r="A66" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C66" s="4" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="3" t="s">
+      <c r="A67" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C67" s="4" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="3" t="s">
+      <c r="A68" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C68" s="4" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="69" spans="1:3">
-      <c r="A69" s="3" t="s">
+      <c r="A69" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B69" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C69" s="4" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="70" spans="1:3">
-      <c r="A70" s="3" t="s">
+      <c r="A70" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C70" s="4" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71" s="3" t="s">
+      <c r="A71" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B71" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C71" s="4" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="3" t="s">
+      <c r="A72" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B72" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C72" s="4" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="3" t="s">
+      <c r="A73" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B73" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C73" s="4" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="74" spans="1:3">
-      <c r="A74" s="3" t="s">
+      <c r="A74" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B74" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C74" s="4" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="3" t="s">
+      <c r="A75" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C75" s="4" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="3" t="s">
+      <c r="A76" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C76" s="4" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" s="3" t="s">
+      <c r="A77" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B77" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C77" s="4" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="78" spans="1:3">
-      <c r="A78" s="3" t="s">
+      <c r="A78" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B78" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="C78" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="79" spans="1:3">
-      <c r="A79" s="3" t="s">
+      <c r="A79" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B79" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C79" s="4" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="3" t="s">
+      <c r="A80" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B80" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="C80" s="4" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="3" t="s">
+      <c r="A81" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B81" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="C81" s="4" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="82" spans="1:3">
-      <c r="A82" s="3" t="s">
+      <c r="A82" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B82" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C82" s="4" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="3" t="s">
+      <c r="A83" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B83" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C83" s="4" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="3" t="s">
+      <c r="A84" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B84" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="C84" s="4" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="85" spans="1:3">
-      <c r="A85" s="3" t="s">
+      <c r="A85" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B85" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C85" s="4" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="86" spans="1:3">
-      <c r="A86" s="3" t="s">
+      <c r="A86" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="B86" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="C86" s="4" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87" s="3" t="s">
+      <c r="A87" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B87" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C87" s="4" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="3" t="s">
+      <c r="A88" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="B88" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="C88" s="4" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="17.5" customHeight="1">
-      <c r="A89" s="3" t="s">
+      <c r="A89" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="B89" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="C89" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="16" customHeight="1">
-      <c r="A90" s="3" t="s">
+      <c r="A90" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="B90" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="C90" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="3" t="s">
+      <c r="A91" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B91" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="C91" s="4" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="3" t="s">
+      <c r="A92" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="B92" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="C92" s="4" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="93" spans="1:3">
-      <c r="A93" s="3" t="s">
+      <c r="A93" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B93" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="C93" s="3" t="s">
+      <c r="C93" s="4" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="94" spans="1:3">
-      <c r="A94" s="3" t="s">
+      <c r="A94" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B94" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="C94" s="4" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="95" spans="1:3">
-      <c r="A95" s="3" t="s">
+      <c r="A95" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="B95" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="C95" s="4" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="3" t="s">
+      <c r="A96" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B96" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="C96" s="4" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="3" t="s">
+      <c r="A97" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B97" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="C97" s="4" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="98" spans="1:3">
-      <c r="A98" s="3" t="s">
+      <c r="A98" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="B98" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="C98" s="4" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="3" t="s">
+      <c r="A99" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B99" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="C99" s="4" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="3" t="s">
+      <c r="A100" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B100" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="C100" s="4" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="101" spans="1:3">
-      <c r="A101" s="3" t="s">
+      <c r="A101" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="B101" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="C101" s="3" t="s">
+      <c r="C101" s="4" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="102" spans="1:3">
-      <c r="A102" s="3" t="s">
+      <c r="A102" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="B102" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="C102" s="3" t="s">
+      <c r="C102" s="4" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="103" spans="1:3">
-      <c r="A103" s="3" t="s">
+      <c r="A103" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="B103" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="C103" s="4" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="3" t="s">
+      <c r="A104" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="B104" s="3" t="s">
+      <c r="B104" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="C104" s="3" t="s">
+      <c r="C104" s="4" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105" s="3" t="s">
+      <c r="A105" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="B105" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="C105" s="4" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="106" spans="1:3">
-      <c r="A106" s="3" t="s">
+      <c r="A106" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="B106" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="C106" s="3" t="s">
+      <c r="C106" s="4" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="107" spans="1:3">
-      <c r="A107" s="3" t="s">
+      <c r="A107" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="B107" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="C107" s="4" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="108" spans="1:3">
-      <c r="A108" s="3" t="s">
+      <c r="A108" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="B108" s="3" t="s">
+      <c r="B108" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="C108" s="3" t="s">
+      <c r="C108" s="4" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="109" spans="1:3">
-      <c r="A109" s="3" t="s">
+      <c r="A109" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="B109" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="C109" s="3" t="s">
+      <c r="C109" s="4" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="110" spans="1:3">
-      <c r="A110" s="3" t="s">
+      <c r="A110" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="B110" s="3" t="s">
+      <c r="B110" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="C110" s="3" t="s">
+      <c r="C110" s="4" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="111" spans="1:3">
-      <c r="A111" s="3" t="s">
+      <c r="A111" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="B111" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C111" s="3" t="s">
+      <c r="C111" s="4" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="112" spans="1:3">
-      <c r="A112" s="3" t="s">
+      <c r="A112" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="B112" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="C112" s="3" t="s">
+      <c r="C112" s="4" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="3" t="s">
+      <c r="A113" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="B113" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="C113" s="3" t="s">
+      <c r="C113" s="4" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="114" spans="1:3">
-      <c r="A114" s="3" t="s">
+      <c r="A114" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="B114" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="C114" s="3" t="s">
+      <c r="C114" s="4" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="115" spans="1:3">
-      <c r="A115" s="3" t="s">
+      <c r="A115" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="B115" s="3"/>
-      <c r="C115" s="3" t="s">
+      <c r="B115" s="4"/>
+      <c r="C115" s="4" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="116" spans="1:3">
-      <c r="A116" s="3" t="s">
+      <c r="A116" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="B116" s="3"/>
-      <c r="C116" s="3" t="s">
+      <c r="B116" s="4"/>
+      <c r="C116" s="4" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="117" spans="1:3">
-      <c r="A117" s="3" t="s">
+      <c r="A117" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="B117" s="3"/>
-      <c r="C117" s="3" t="s">
+      <c r="B117" s="4"/>
+      <c r="C117" s="4" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="118" spans="1:3">
-      <c r="A118" s="3" t="s">
+      <c r="A118" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="B118" s="3"/>
-      <c r="C118" s="3" t="s">
+      <c r="B118" s="4"/>
+      <c r="C118" s="4" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="119" spans="1:3">
-      <c r="A119" s="3" t="s">
+      <c r="A119" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="B119" s="3"/>
-      <c r="C119" s="3" t="s">
+      <c r="B119" s="4"/>
+      <c r="C119" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="120" spans="1:3">
-      <c r="A120" s="3" t="s">
+      <c r="A120" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="B120" s="3"/>
-      <c r="C120" s="3" t="s">
+      <c r="B120" s="4"/>
+      <c r="C120" s="4" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="121" spans="1:3">
-      <c r="A121" s="3" t="s">
+      <c r="A121" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="B121" s="3"/>
-      <c r="C121" s="3" t="s">
+      <c r="B121" s="4"/>
+      <c r="C121" s="4" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="122" spans="1:3">
-      <c r="A122" s="3" t="s">
+      <c r="A122" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="B122" s="3"/>
-      <c r="C122" s="3" t="s">
+      <c r="B122" s="4"/>
+      <c r="C122" s="4" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="123" spans="1:3">
-      <c r="A123" s="3" t="s">
+      <c r="A123" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="B123" s="3"/>
-      <c r="C123" s="3" t="s">
+      <c r="B123" s="4"/>
+      <c r="C123" s="4" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="3" t="s">
+      <c r="A124" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="B124" s="3"/>
-      <c r="C124" s="3" t="s">
+      <c r="B124" s="4"/>
+      <c r="C124" s="4" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="125" spans="1:3">
-      <c r="A125" s="3" t="s">
+      <c r="A125" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="B125" s="3"/>
-      <c r="C125" s="3" t="s">
+      <c r="B125" s="4"/>
+      <c r="C125" s="4" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="126" spans="1:3">
-      <c r="A126" s="3" t="s">
+      <c r="A126" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="B126" s="3"/>
-      <c r="C126" s="3" t="s">
+      <c r="B126" s="4"/>
+      <c r="C126" s="4" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="127" spans="1:3">
-      <c r="A127" s="3" t="s">
+      <c r="A127" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="B127" s="3"/>
-      <c r="C127" s="3" t="s">
+      <c r="B127" s="4"/>
+      <c r="C127" s="4" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="128" spans="1:3">
-      <c r="A128" s="3" t="s">
+      <c r="A128" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="B128" s="3"/>
-      <c r="C128" s="3" t="s">
+      <c r="B128" s="4"/>
+      <c r="C128" s="4" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="129" spans="1:3">
-      <c r="A129" s="3" t="s">
+      <c r="A129" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="B129" s="3"/>
-      <c r="C129" s="3" t="s">
+      <c r="B129" s="4"/>
+      <c r="C129" s="4" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="130" spans="1:3">
-      <c r="A130" s="3" t="s">
+      <c r="A130" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B130" s="3"/>
-      <c r="C130" s="3" t="s">
+      <c r="B130" s="4"/>
+      <c r="C130" s="4" t="s">
         <v>4</v>
       </c>
     </row>

--- a/StriversSheet/leetcode_problem_links_topics_plain.xlsx
+++ b/StriversSheet/leetcode_problem_links_topics_plain.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NFRAC\Laboratory\Projects\Java\LeetCodeSolutions\StriversSheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38A5A7DE-8F89-4E53-970F-82657E97D287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C349AD5F-FFA7-46D5-8A56-7F40420B666C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1080,7 +1080,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1114,6 +1114,19 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1137,10 +1150,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1157,8 +1171,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1373,7 +1394,7 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="64.83203125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="112.1640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="76" style="3" customWidth="1"/>
     <col min="3" max="3" width="81.6640625" style="3" customWidth="1"/>
     <col min="4" max="16384" width="8.6640625" style="3"/>
   </cols>
@@ -1393,7 +1414,7 @@
       <c r="A2" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="7" t="s">
         <v>319</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -1404,7 +1425,7 @@
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -1415,7 +1436,7 @@
       <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -1492,7 +1513,7 @@
       <c r="A11" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C11" s="4" t="s">
@@ -1503,7 +1524,7 @@
       <c r="A12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -1547,7 +1568,7 @@
       <c r="A16" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="6" t="s">
         <v>41</v>
       </c>
       <c r="C16" s="4" t="s">
@@ -1558,7 +1579,7 @@
       <c r="A17" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C17" s="4" t="s">
@@ -1569,7 +1590,7 @@
       <c r="A18" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="6" t="s">
         <v>46</v>
       </c>
       <c r="C18" s="4" t="s">
@@ -1580,7 +1601,7 @@
       <c r="A19" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="6" t="s">
         <v>49</v>
       </c>
       <c r="C19" s="4" t="s">
@@ -1679,7 +1700,7 @@
       <c r="A28" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="6" t="s">
         <v>74</v>
       </c>
       <c r="C28" s="4" t="s">
@@ -1690,7 +1711,7 @@
       <c r="A29" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="6" t="s">
         <v>77</v>
       </c>
       <c r="C29" s="4" t="s">
@@ -1701,7 +1722,7 @@
       <c r="A30" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="6" t="s">
         <v>80</v>
       </c>
       <c r="C30" s="4" t="s">
@@ -2053,7 +2074,7 @@
       <c r="A62" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="6" t="s">
         <v>166</v>
       </c>
       <c r="C62" s="4" t="s">
@@ -2086,7 +2107,7 @@
       <c r="A65" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" s="6" t="s">
         <v>175</v>
       </c>
       <c r="C65" s="4" t="s">
@@ -2108,7 +2129,7 @@
       <c r="A67" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="6" t="s">
         <v>181</v>
       </c>
       <c r="C67" s="4" t="s">
@@ -2328,7 +2349,7 @@
       <c r="A87" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="B87" s="6" t="s">
         <v>234</v>
       </c>
       <c r="C87" s="4" t="s">
@@ -2504,7 +2525,7 @@
       <c r="A103" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="B103" s="6" t="s">
         <v>278</v>
       </c>
       <c r="C103" s="4" t="s">
@@ -2559,7 +2580,7 @@
       <c r="A108" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="B108" s="4" t="s">
+      <c r="B108" s="6" t="s">
         <v>291</v>
       </c>
       <c r="C108" s="4" t="s">
@@ -2614,7 +2635,7 @@
       <c r="A113" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="B113" s="4" t="s">
+      <c r="B113" s="6" t="s">
         <v>334</v>
       </c>
       <c r="C113" s="4" t="s">
@@ -2625,7 +2646,7 @@
       <c r="A114" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="B114" s="4" t="s">
+      <c r="B114" s="6" t="s">
         <v>341</v>
       </c>
       <c r="C114" s="4" t="s">
@@ -2777,6 +2798,28 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{34654A2A-27DE-484F-8192-3AF0CFE543F0}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{4C106444-325B-4696-86B0-F212798F7973}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{76DAAF99-0463-4316-958A-702EF47FA94E}"/>
+    <hyperlink ref="B11" r:id="rId4" xr:uid="{CF568CEF-53B7-4099-A868-BF923F19455E}"/>
+    <hyperlink ref="B12" r:id="rId5" xr:uid="{A82B0611-EA2A-4529-9997-0DC35A83C221}"/>
+    <hyperlink ref="B16" r:id="rId6" xr:uid="{013A4583-5A81-424B-915A-223E2EBB735E}"/>
+    <hyperlink ref="B17" r:id="rId7" xr:uid="{8DD9003F-C779-403F-84A7-925366C7AA7B}"/>
+    <hyperlink ref="B18" r:id="rId8" xr:uid="{17969309-E20D-4301-8E49-9ACDCDE44E60}"/>
+    <hyperlink ref="B19" r:id="rId9" xr:uid="{D5530BE8-2CE1-49BA-BCAE-A4AC5B3B10DF}"/>
+    <hyperlink ref="B28" r:id="rId10" xr:uid="{02444E31-0EB4-4757-B508-3BF00306E97F}"/>
+    <hyperlink ref="B29" r:id="rId11" xr:uid="{2745FFF7-887C-4516-B5D5-D17E1A0725C1}"/>
+    <hyperlink ref="B30" r:id="rId12" xr:uid="{CB35FA6E-8665-49E8-851E-355FB16BEDB7}"/>
+    <hyperlink ref="B62" r:id="rId13" xr:uid="{AB060AAE-9224-4EFF-A7B6-4DFE8B90800E}"/>
+    <hyperlink ref="B65" r:id="rId14" xr:uid="{24EDC953-99A1-45F9-9BA3-7296FE15D5BD}"/>
+    <hyperlink ref="B67" r:id="rId15" xr:uid="{8DDF907C-EB06-40B2-AAAE-FD1C908D38CA}"/>
+    <hyperlink ref="B87" r:id="rId16" xr:uid="{27C160E2-04CB-4E47-A9C1-6BE10A060198}"/>
+    <hyperlink ref="B103" r:id="rId17" xr:uid="{E632FA28-F557-41F3-A733-D67402C609FC}"/>
+    <hyperlink ref="B108" r:id="rId18" xr:uid="{B98D37B3-9759-43A9-8F0E-DD2B11D400DA}"/>
+    <hyperlink ref="B114" r:id="rId19" xr:uid="{2BC065E6-962B-4602-8BEC-FA659E6E7397}"/>
+    <hyperlink ref="B113" r:id="rId20" xr:uid="{BDAA1EF8-3E15-49A2-8824-F937AA314222}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
